--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251201_201420.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
